--- a/data/trans_orig/P1412-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1412-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de angina de pecho en 2012</t>
+          <t>Población con diagnóstico de angina de pecho en 2012 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>950</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10248</t>
+          <t>8546</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7440</t>
+          <t>6574</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12596</t>
+          <t>11885</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>284490</t>
+          <t>286192</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>293751</t>
+          <t>293788</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>279805</t>
+          <t>280671</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>569387</t>
+          <t>570098</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>579972</t>
+          <t>579974</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7614</t>
+          <t>6999</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>990</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8732</t>
+          <t>8437</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11630</t>
+          <t>11615</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>497913</t>
+          <t>498528</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>515033</t>
+          <t>515328</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>522766</t>
+          <t>522775</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1017662</t>
+          <t>1017677</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1027275</t>
+          <t>1027272</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1418,97 +1418,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1944</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5549</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>1102</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4915</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>6636</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1102</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>5534</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>322102</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>324046</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>336105</t>
+          <t>335471</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>659532</t>
+          <t>658430</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7672</t>
+          <t>7706</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>2086</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11128</t>
+          <t>12123</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3134</t>
+          <t>3214</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14204</t>
+          <t>14878</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>366310</t>
+          <t>366276</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>377823</t>
+          <t>376828</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>387026</t>
+          <t>386865</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>748729</t>
+          <t>748055</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>759799</t>
+          <t>759719</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,58%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>2087</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15776</t>
+          <t>15636</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>4817</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2198</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16711</t>
+          <t>15213</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>196842</t>
+          <t>196982</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210564</t>
+          <t>210531</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>213359</t>
+          <t>214774</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>415498</t>
+          <t>416996</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>430011</t>
+          <t>430142</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>973</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8523</t>
+          <t>8245</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>977</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9336</t>
+          <t>8362</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>271974</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>273981</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>269573</t>
+          <t>269851</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>277128</t>
+          <t>277123</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>542741</t>
+          <t>543715</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>551106</t>
+          <t>551100</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10516</t>
+          <t>12017</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11769</t>
+          <t>10876</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4221</t>
+          <t>4475</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17376</t>
+          <t>18756</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>652272</t>
+          <t>650771</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>660804</t>
+          <t>660787</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>681137</t>
+          <t>682030</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>691590</t>
+          <t>691599</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1338318</t>
+          <t>1336938</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1351473</t>
+          <t>1351219</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9914</t>
+          <t>11042</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10997</t>
+          <t>11185</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4219</t>
+          <t>4282</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16439</t>
+          <t>16665</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>769184</t>
+          <t>768056</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>778012</t>
+          <t>777961</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>810398</t>
+          <t>810210</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>820229</t>
+          <t>820318</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1584054</t>
+          <t>1583828</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1596274</t>
+          <t>1596211</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>14954</t>
+          <t>14015</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>35461</t>
+          <t>34907</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>16551</t>
+          <t>16104</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>37435</t>
+          <t>37053</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>34544</t>
+          <t>34978</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>63667</t>
+          <t>64582</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3391318</t>
+          <t>3391872</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3411825</t>
+          <t>3412764</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3515533</t>
+          <t>3515915</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3536417</t>
+          <t>3536864</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6916080</t>
+          <t>6915165</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6945203</t>
+          <t>6944769</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -3860,7 +3860,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de angina de pecho en 2016</t>
+          <t>Población con diagnóstico de angina de pecho en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7136</t>
+          <t>6534</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5644</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7972</t>
+          <t>9390</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -4168,7 +4168,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>286625</t>
+          <t>287227</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>283059</t>
+          <t>283493</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>574492</t>
+          <t>573074</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>1766</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11538</t>
+          <t>11144</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>996</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8697</t>
+          <t>8335</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3321</t>
+          <t>3306</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15619</t>
+          <t>15669</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>491037</t>
+          <t>491431</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>500622</t>
+          <t>500809</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>514387</t>
+          <t>514749</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>522087</t>
+          <t>522088</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1010040</t>
+          <t>1009990</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1022338</t>
+          <t>1022353</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4773</t>
+          <t>4815</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4776,47 +4776,47 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1531</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1939</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1531</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5278</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>313792</t>
+          <t>313750</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>334370</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>336309</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>649596</t>
+          <t>649567</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1690</t>
+          <t>1801</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10649</t>
+          <t>10945</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>937</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9925</t>
+          <t>9237</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3964</t>
+          <t>3903</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16273</t>
+          <t>14428</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>359315</t>
+          <t>359019</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>368274</t>
+          <t>368163</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>377358</t>
+          <t>378046</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>386344</t>
+          <t>386346</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>740974</t>
+          <t>742819</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>753283</t>
+          <t>753344</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4391</t>
+          <t>4113</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5462,62 +5462,62 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>814</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>1873</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>4098</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>814</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>4669</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>206830</t>
+          <t>207108</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>216714</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>218587</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>425139</t>
+          <t>425710</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>6157</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,62 +5805,62 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1781</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1985</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>6895</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1781</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>5692</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>257459</t>
+          <t>256966</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>271130</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>273115</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>530546</t>
+          <t>529343</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1785</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13362</t>
+          <t>12716</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3543</t>
+          <t>3516</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15430</t>
+          <t>16377</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7132</t>
+          <t>6790</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24015</t>
+          <t>23899</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>643196</t>
+          <t>643842</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>654773</t>
+          <t>655374</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>675864</t>
+          <t>674917</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>687751</t>
+          <t>687778</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1323837</t>
+          <t>1323953</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1340720</t>
+          <t>1341062</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2091</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11667</t>
+          <t>11766</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1068</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9643</t>
+          <t>8844</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4778</t>
+          <t>4606</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17355</t>
+          <t>16732</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>766916</t>
+          <t>766817</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>776569</t>
+          <t>776492</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>816524</t>
+          <t>817323</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>825099</t>
+          <t>825101</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1587395</t>
+          <t>1588018</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1599972</t>
+          <t>1600144</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,71%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>17034</t>
+          <t>16843</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>39249</t>
+          <t>37325</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>11093</t>
+          <t>10542</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>29579</t>
+          <t>30233</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>33241</t>
+          <t>33386</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>60229</t>
+          <t>60484</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3355101</t>
+          <t>3357025</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3377316</t>
+          <t>3377507</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3514963</t>
+          <t>3514309</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3533449</t>
+          <t>3534000</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6878663</t>
+          <t>6878408</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6905651</t>
+          <t>6905506</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7183,7 +7183,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de angina de pecho en 2023</t>
+          <t>Población con diagnóstico de angina de pecho en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7383,7 +7383,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6455</t>
+          <t>5868</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>2506</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>408</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6996</t>
+          <t>6421</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -7491,7 +7491,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>304988</t>
+          <t>305575</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>287531</t>
+          <t>287129</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>594081</t>
+          <t>594656</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>600664</t>
+          <t>600669</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>925</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>8609</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7736,12 +7736,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>577</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5576</t>
+          <t>5715</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7771,12 +7771,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2790</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11947</t>
+          <t>11451</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -7834,12 +7834,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>507011</t>
+          <t>507426</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>515139</t>
+          <t>515110</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>507984</t>
+          <t>507845</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>512967</t>
+          <t>512983</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1017648</t>
+          <t>1018144</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1026805</t>
+          <t>1026961</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7919,12 +7919,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -8064,12 +8064,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9318</t>
+          <t>9418</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8079,12 +8079,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1634</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7356</t>
+          <t>7919</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8114,12 +8114,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4679</t>
+          <t>4694</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13559</t>
+          <t>14247</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -8177,12 +8177,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>306732</t>
+          <t>306632</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>314102</t>
+          <t>314061</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8192,12 +8192,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>341772</t>
+          <t>341209</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>347540</t>
+          <t>347494</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8227,12 +8227,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>651619</t>
+          <t>650931</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>660499</t>
+          <t>660484</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8262,12 +8262,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -8407,12 +8407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2628</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12370</t>
+          <t>12371</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -8447,7 +8447,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2133</t>
+          <t>2170</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8462,7 +8462,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3124</t>
+          <t>2874</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13685</t>
+          <t>13422</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -8520,12 +8520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>300187</t>
+          <t>300186</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>309929</t>
+          <t>310053</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8555,7 +8555,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>473585</t>
+          <t>473548</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>774589</t>
+          <t>774852</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>785150</t>
+          <t>785400</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -8750,97 +8750,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>716</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1225</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>716</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2586</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>2497</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>716</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>2690</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -8863,12 +8863,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>177517</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8898,7 +8898,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>205289</t>
+          <t>205672</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8933,7 +8933,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>383927</t>
+          <t>384120</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9093,12 +9093,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2193</t>
+          <t>2154</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8512</t>
+          <t>8796</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9128,12 +9128,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>587</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4768</t>
+          <t>4736</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9143,12 +9143,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3682</t>
+          <t>3786</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11337</t>
+          <t>11234</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -9206,12 +9206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>261124</t>
+          <t>260840</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>267443</t>
+          <t>267482</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9241,12 +9241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>251619</t>
+          <t>251651</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>255811</t>
+          <t>255800</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9256,12 +9256,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>514686</t>
+          <t>514789</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>522341</t>
+          <t>522237</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -9436,12 +9436,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2729</t>
+          <t>2984</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12736</t>
+          <t>14215</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9471,12 +9471,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1428</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9157</t>
+          <t>8706</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5581</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18671</t>
+          <t>18712</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9549,12 +9549,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>609503</t>
+          <t>608024</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>619510</t>
+          <t>619255</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9584,12 +9584,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>839101</t>
+          <t>839552</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>846994</t>
+          <t>846830</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9599,12 +9599,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1451826</t>
+          <t>1451785</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1464916</t>
+          <t>1464884</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9784,7 +9784,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7535</t>
+          <t>7771</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1667</t>
+          <t>1770</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8018</t>
+          <t>8326</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12479</t>
+          <t>12997</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -9892,7 +9892,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>921185</t>
+          <t>920949</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>707374</t>
+          <t>707066</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>713725</t>
+          <t>713622</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1631633</t>
+          <t>1631115</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1640788</t>
+          <t>1641126</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,82%</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>20729</t>
+          <t>21197</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>41575</t>
+          <t>42526</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>12552</t>
+          <t>12410</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>25532</t>
+          <t>25356</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10177,7 +10177,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>35847</t>
+          <t>36207</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>60742</t>
+          <t>60708</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,7 +10207,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3413847</t>
+          <t>3412896</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3434693</t>
+          <t>3434225</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3630420</t>
+          <t>3630596</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3643400</t>
+          <t>3643542</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,7 +10285,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7050632</t>
+          <t>7050666</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7075527</t>
+          <t>7075167</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1412-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1412-Provincia-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>925</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8546</t>
+          <t>8681</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6574</t>
+          <t>6544</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2072</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11885</t>
+          <t>12541</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>286192</t>
+          <t>286057</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>293788</t>
+          <t>293813</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>280671</t>
+          <t>280701</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>570098</t>
+          <t>569442</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>579974</t>
+          <t>579911</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6999</t>
+          <t>6359</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>994</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8437</t>
+          <t>8812</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11615</t>
+          <t>11501</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>498528</t>
+          <t>499168</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>515328</t>
+          <t>514953</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>522775</t>
+          <t>522771</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1017677</t>
+          <t>1017791</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1027272</t>
+          <t>1027298</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,81%</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5549</t>
+          <t>6037</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6636</t>
+          <t>5514</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>335471</t>
+          <t>334983</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>658430</t>
+          <t>659552</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7706</t>
+          <t>7715</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2086</t>
+          <t>1956</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12123</t>
+          <t>11849</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3214</t>
+          <t>3176</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14878</t>
+          <t>15243</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>366276</t>
+          <t>366267</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>376828</t>
+          <t>377102</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>386865</t>
+          <t>386995</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>748055</t>
+          <t>747690</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>759719</t>
+          <t>759757</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2087</t>
+          <t>1823</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15636</t>
+          <t>14546</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4817</t>
+          <t>5384</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2067</t>
+          <t>2073</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15213</t>
+          <t>16181</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>196982</t>
+          <t>198072</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210531</t>
+          <t>210795</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>214774</t>
+          <t>214207</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>416996</t>
+          <t>416028</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>430142</t>
+          <t>430136</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>970</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8245</t>
+          <t>8235</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>976</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8362</t>
+          <t>8506</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>269851</t>
+          <t>269861</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>277123</t>
+          <t>277126</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>543715</t>
+          <t>543571</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>551100</t>
+          <t>551101</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12017</t>
+          <t>11404</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10876</t>
+          <t>10569</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4475</t>
+          <t>4420</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18756</t>
+          <t>18093</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>650771</t>
+          <t>651384</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>660787</t>
+          <t>660770</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>682030</t>
+          <t>682337</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>691599</t>
+          <t>691852</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1336938</t>
+          <t>1337601</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1351219</t>
+          <t>1351274</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11042</t>
+          <t>10910</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>1157</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11185</t>
+          <t>10581</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4282</t>
+          <t>3420</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16665</t>
+          <t>16048</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>768056</t>
+          <t>768188</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>777961</t>
+          <t>777970</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>810210</t>
+          <t>810814</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>820318</t>
+          <t>820238</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1583828</t>
+          <t>1584445</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1596211</t>
+          <t>1597073</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>14015</t>
+          <t>14192</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>34907</t>
+          <t>34240</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>16104</t>
+          <t>16087</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>37053</t>
+          <t>36747</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>34978</t>
+          <t>35976</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>64582</t>
+          <t>65540</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3391872</t>
+          <t>3392539</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3412764</t>
+          <t>3412587</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3515915</t>
+          <t>3516221</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3536864</t>
+          <t>3536881</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6915165</t>
+          <t>6914207</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6944769</t>
+          <t>6943771</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6534</t>
+          <t>7410</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>5820</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9390</t>
+          <t>7606</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -4168,7 +4168,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>287227</t>
+          <t>286351</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>283493</t>
+          <t>282883</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>573074</t>
+          <t>574858</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1766</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11144</t>
+          <t>13105</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8335</t>
+          <t>9624</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3306</t>
+          <t>3062</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15669</t>
+          <t>15428</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>491431</t>
+          <t>489470</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>500809</t>
+          <t>500616</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>514749</t>
+          <t>513460</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>522088</t>
+          <t>522084</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1009990</t>
+          <t>1010231</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1022353</t>
+          <t>1022597</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4815</t>
+          <t>5421</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5307</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>313750</t>
+          <t>313144</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>649567</t>
+          <t>649449</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1801</t>
+          <t>1857</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10945</t>
+          <t>11672</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>939</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9237</t>
+          <t>9553</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3903</t>
+          <t>3868</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14428</t>
+          <t>15393</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>359019</t>
+          <t>358292</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>368163</t>
+          <t>368107</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>378046</t>
+          <t>377730</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>386346</t>
+          <t>386344</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>742819</t>
+          <t>741854</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>753344</t>
+          <t>753379</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4113</t>
+          <t>4123</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4098</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>207108</t>
+          <t>207098</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>425710</t>
+          <t>425720</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6157</t>
+          <t>6370</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6895</t>
+          <t>6542</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>256966</t>
+          <t>256753</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>529343</t>
+          <t>529696</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12716</t>
+          <t>11987</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3516</t>
+          <t>3482</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16377</t>
+          <t>16642</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6790</t>
+          <t>6780</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23899</t>
+          <t>22869</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>643842</t>
+          <t>644571</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>655374</t>
+          <t>655358</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>674917</t>
+          <t>674652</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>687778</t>
+          <t>687812</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1323953</t>
+          <t>1324983</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1341062</t>
+          <t>1341072</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2091</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11766</t>
+          <t>12640</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8844</t>
+          <t>9411</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4606</t>
+          <t>4116</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16732</t>
+          <t>16783</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>766817</t>
+          <t>765943</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>776492</t>
+          <t>776586</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>817323</t>
+          <t>816756</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>825101</t>
+          <t>825097</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1588018</t>
+          <t>1587967</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1600144</t>
+          <t>1600634</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>16843</t>
+          <t>16958</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>37325</t>
+          <t>38075</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10542</t>
+          <t>11125</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>30233</t>
+          <t>30679</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>33386</t>
+          <t>31245</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>60484</t>
+          <t>59836</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3357025</t>
+          <t>3356275</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3377507</t>
+          <t>3377392</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3514309</t>
+          <t>3513863</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3534000</t>
+          <t>3533417</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6878408</t>
+          <t>6879056</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6905506</t>
+          <t>6907647</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1567</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5868</t>
+          <t>5319</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>469</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2506</t>
+          <t>2445</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7443,22 +7443,22 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>2036</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>469</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6421</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -7486,27 +7486,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>309727</t>
+          <t>317278</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>305575</t>
+          <t>313526</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7521,27 +7521,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>289226</t>
+          <t>315592</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>287129</t>
+          <t>313616</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -7556,27 +7556,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>598952</t>
+          <t>632870</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>594656</t>
+          <t>629549</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>600669</t>
+          <t>634437</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7599,17 +7599,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7634,17 +7634,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7669,17 +7669,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3599</t>
+          <t>3781</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>948</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8609</t>
+          <t>9649</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7751,22 +7751,22 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2440</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>591</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>6248</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7786,17 +7786,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>5955</t>
+          <t>6221</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2786</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11451</t>
+          <t>12057</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -7829,27 +7829,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>512436</t>
+          <t>524523</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>507426</t>
+          <t>518655</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>515110</t>
+          <t>527356</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7864,27 +7864,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>511204</t>
+          <t>542647</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>507845</t>
+          <t>538839</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>512983</t>
+          <t>544496</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7899,17 +7899,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1023640</t>
+          <t>1067170</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1018144</t>
+          <t>1061334</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1026961</t>
+          <t>1070605</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7942,17 +7942,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>516035</t>
+          <t>528304</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>516035</t>
+          <t>528304</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>516035</t>
+          <t>528304</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7977,17 +7977,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>513560</t>
+          <t>545087</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>513560</t>
+          <t>545087</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>513560</t>
+          <t>545087</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8012,17 +8012,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1029595</t>
+          <t>1073391</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1029595</t>
+          <t>1073391</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1029595</t>
+          <t>1073391</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8059,22 +8059,22 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4699</t>
+          <t>4617</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9418</t>
+          <t>9441</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8094,32 +8094,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3720</t>
+          <t>3736</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1634</t>
+          <t>1551</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7919</t>
+          <t>7648</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8129,27 +8129,27 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>8419</t>
+          <t>8353</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4694</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14247</t>
+          <t>14405</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -8172,27 +8172,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>311351</t>
+          <t>311376</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>306632</t>
+          <t>306552</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>314061</t>
+          <t>314005</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8207,32 +8207,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>345408</t>
+          <t>352645</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>341209</t>
+          <t>348733</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>347494</t>
+          <t>354830</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8242,22 +8242,22 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>656759</t>
+          <t>664022</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>650931</t>
+          <t>657970</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>660484</t>
+          <t>667512</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -8267,7 +8267,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -8285,17 +8285,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8355,17 +8355,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8402,32 +8402,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5977</t>
+          <t>6845</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>3314</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12371</t>
+          <t>14349</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8437,7 +8437,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>431</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -8447,12 +8447,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2170</t>
+          <t>2373</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -8462,42 +8462,42 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>7275</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>3658</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>15513</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>0,46%</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>6391</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>2874</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>13422</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -8515,32 +8515,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>306580</t>
+          <t>366300</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>300186</t>
+          <t>358796</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>310053</t>
+          <t>369831</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8550,67 +8550,67 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>475304</t>
+          <t>421530</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>473548</t>
+          <t>419588</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,9%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
+          <t>99,44%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>881</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>787832</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>779594</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>791449</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>99,08%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>98,05%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>99,54%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>881</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>781883</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>774852</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>785400</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>99,19%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>98,3%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -8628,17 +8628,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8663,17 +8663,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8698,17 +8698,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8780,7 +8780,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>730</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -8790,12 +8790,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2203</t>
+          <t>2534</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -8805,7 +8805,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>730</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2497</t>
+          <t>2315</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -8858,7 +8858,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -8893,27 +8893,27 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>207159</t>
+          <t>225693</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>205672</t>
+          <t>223889</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>207875</t>
+          <t>226423</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8928,27 +8928,27 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>385901</t>
+          <t>431357</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>384120</t>
+          <t>429772</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>386617</t>
+          <t>432087</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -8971,17 +8971,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9006,17 +9006,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>207875</t>
+          <t>226423</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>207875</t>
+          <t>226423</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>207875</t>
+          <t>226423</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9041,17 +9041,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>386617</t>
+          <t>432087</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>386617</t>
+          <t>432087</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>386617</t>
+          <t>432087</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9088,22 +9088,22 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4640</t>
+          <t>4619</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2154</t>
+          <t>2159</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8796</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9123,32 +9123,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>715</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4736</t>
+          <t>4499</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9158,32 +9158,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>6528</t>
+          <t>6434</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3786</t>
+          <t>3429</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11234</t>
+          <t>10848</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -9201,27 +9201,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>264996</t>
+          <t>266088</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>260840</t>
+          <t>261706</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>267482</t>
+          <t>268548</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9236,32 +9236,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>254499</t>
+          <t>261284</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>251651</t>
+          <t>258600</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>255800</t>
+          <t>262384</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9271,32 +9271,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>519495</t>
+          <t>527372</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>514789</t>
+          <t>522958</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>522237</t>
+          <t>530377</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -9314,17 +9314,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9349,17 +9349,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9384,17 +9384,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9431,32 +9431,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>6599</t>
+          <t>7971</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2984</t>
+          <t>3690</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14215</t>
+          <t>15112</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9466,32 +9466,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>4405</t>
+          <t>6790</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>3314</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8706</t>
+          <t>12058</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9501,32 +9501,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>11004</t>
+          <t>14761</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5613</t>
+          <t>8589</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18712</t>
+          <t>22131</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -9544,32 +9544,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>615640</t>
+          <t>709449</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>608024</t>
+          <t>702308</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>619255</t>
+          <t>713730</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9579,32 +9579,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>843853</t>
+          <t>763165</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>839552</t>
+          <t>757897</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>846830</t>
+          <t>766641</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9614,32 +9614,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1459493</t>
+          <t>1472615</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1451785</t>
+          <t>1465245</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1464884</t>
+          <t>1478787</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -9657,17 +9657,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>622239</t>
+          <t>717420</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>622239</t>
+          <t>717420</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>622239</t>
+          <t>717420</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9692,17 +9692,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>848258</t>
+          <t>769955</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>848258</t>
+          <t>769955</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>848258</t>
+          <t>769955</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9727,17 +9727,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1470497</t>
+          <t>1487376</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1470497</t>
+          <t>1487376</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1470497</t>
+          <t>1487376</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9774,32 +9774,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2923</t>
+          <t>3272</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7771</t>
+          <t>8507</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9809,67 +9809,67 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>4561</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>1876</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8326</t>
+          <t>8778</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>7833</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>4032</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>13960</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>0,25%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>6946</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>2986</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>12997</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -9887,32 +9887,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>925797</t>
+          <t>794800</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>920949</t>
+          <t>789565</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>928086</t>
+          <t>796941</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9922,67 +9922,67 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>711370</t>
+          <t>826048</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>707066</t>
+          <t>821831</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>713622</t>
+          <t>828733</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
+          <t>99,77%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>1812</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>1620848</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>1614721</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>1624649</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>99,52%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>99,14%</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
           <t>99,75%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>1637166</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>1631115</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>1641126</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>99,58%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>99,21%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>99,82%</t>
         </is>
       </c>
     </row>
@@ -10000,17 +10000,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10035,17 +10035,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10070,17 +10070,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10117,32 +10117,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>30153</t>
+          <t>32671</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>21197</t>
+          <t>23976</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>42526</t>
+          <t>45421</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10152,32 +10152,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>17930</t>
+          <t>20972</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>12410</t>
+          <t>14728</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>25356</t>
+          <t>28149</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10187,32 +10187,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>48083</t>
+          <t>53643</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>36207</t>
+          <t>42561</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>60708</t>
+          <t>67365</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -10230,32 +10230,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3425269</t>
+          <t>3495481</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3412896</t>
+          <t>3482731</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3434225</t>
+          <t>3504176</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10265,32 +10265,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3638022</t>
+          <t>3708605</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3630596</t>
+          <t>3701428</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3643542</t>
+          <t>3714849</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10300,32 +10300,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>7063291</t>
+          <t>7204086</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7050666</t>
+          <t>7190364</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7075167</t>
+          <t>7215168</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -10343,17 +10343,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3455422</t>
+          <t>3528152</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3455422</t>
+          <t>3528152</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3455422</t>
+          <t>3528152</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10378,17 +10378,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3655952</t>
+          <t>3729577</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3655952</t>
+          <t>3729577</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3655952</t>
+          <t>3729577</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10413,17 +10413,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7111374</t>
+          <t>7257729</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7111374</t>
+          <t>7257729</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7111374</t>
+          <t>7257729</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
